--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-diagnostic-report-imaging-document.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-diagnostic-report-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T11:43:27+00:00</t>
+    <t>2026-07-01T12:03:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-diagnostic-report-imaging-document.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-diagnostic-report-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T12:03:19+00:00</t>
+    <t>2026-07-03T07:33:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -678,7 +678,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-resultat-type-cisis|20260420150250</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-resultat-type-cisis|20260619134042</t>
   </si>
   <si>
     <t>OBR-24</t>
@@ -703,7 +703,7 @@
     <t>A code or name that describes this diagnostic report.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-code-document-imagerie-cisis|20260420150249</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-code-document-imagerie-cisis|20260619134041</t>
   </si>
   <si>
     <t>Event.code</t>

--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-diagnostic-report-imaging-document.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-diagnostic-report-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-03T07:33:59+00:00</t>
+    <t>2026-07-08T09:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-diagnostic-report-imaging-document.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-diagnostic-report-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T09:43:12+00:00</t>
+    <t>2026-07-08T10:07:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
